--- a/reference/sample-output/scoring-v2-EXAMPLE.xlsx
+++ b/reference/sample-output/scoring-v2-EXAMPLE.xlsx
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Framework 2.0.1 · generated 2026-09-29</t>
+          <t>Framework 2.0.2 · generated 2026-09-29</t>
         </is>
       </c>
     </row>
